--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6D122C-1276-1140-BB80-6041951D419B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FFA1A7-F123-0E48-8508-10CF33C277BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Week</t>
   </si>
@@ -92,9 +92,6 @@
     <t>Resources</t>
   </si>
   <si>
-    <t>/modules/01-Module.html</t>
-  </si>
-  <si>
     <t>/modules/02-Module.html</t>
   </si>
   <si>
@@ -176,16 +173,16 @@
     <t>Linear regression</t>
   </si>
   <si>
-    <t>Introduction to the course</t>
-  </si>
-  <si>
-    <t>Introduction to Modeling</t>
-  </si>
-  <si>
     <t>Multiple regression</t>
   </si>
   <si>
     <t>Missing data</t>
+  </si>
+  <si>
+    <t>Introduction to the Modeling</t>
+  </si>
+  <si>
+    <t>Project Proposal</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
         <v>14</v>
@@ -1120,10 +1117,13 @@
         <v>46265</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1143,7 +1143,7 @@
         <v>46272</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>46286</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>22</v>
@@ -1221,7 +1221,7 @@
         <v>46293</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>23</v>
@@ -1247,7 +1247,7 @@
         <v>46300</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>24</v>
@@ -1273,7 +1273,7 @@
         <v>46307</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>25</v>
@@ -1299,7 +1299,7 @@
         <v>46314</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>26</v>
@@ -1325,7 +1325,7 @@
         <v>46321</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>27</v>
@@ -1351,7 +1351,7 @@
         <v>46328</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
@@ -1377,7 +1377,7 @@
         <v>46335</v>
       </c>
       <c r="E12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>29</v>
@@ -1403,13 +1403,7 @@
         <v>46342</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1423,7 +1417,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1443,10 +1437,10 @@
         <v>46356</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1469,7 +1463,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FFA1A7-F123-0E48-8508-10CF33C277BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA48E43-7BEE-F54B-BF68-736DF189B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
@@ -92,45 +92,6 @@
     <t>Resources</t>
   </si>
   <si>
-    <t>/modules/02-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/03-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/04-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/05-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/06-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/07-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/08-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/09-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/10-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/11-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/12-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/13-Module.html</t>
-  </si>
-  <si>
-    <t>/modules/14-Module.html</t>
-  </si>
-  <si>
     <t>Topic</t>
   </si>
   <si>
@@ -183,6 +144,45 @@
   </si>
   <si>
     <t>Project Proposal</t>
+  </si>
+  <si>
+    <t>/modules/01-Intro_to_Modeling.html</t>
+  </si>
+  <si>
+    <t>/modules/02-Linear_Regression.html</t>
+  </si>
+  <si>
+    <t>/modules/03-Multiple_Regression.html</t>
+  </si>
+  <si>
+    <t>/modules/04-Logistic_Regression.html</t>
+  </si>
+  <si>
+    <t>/modules/05-Generative_Models.html</t>
+  </si>
+  <si>
+    <t>/modules/06-Resampling_Methods.html</t>
+  </si>
+  <si>
+    <t>/modules/07-Tree_Models.html</t>
+  </si>
+  <si>
+    <t>/modules/08-Bagging_and_Random_Forests.html</t>
+  </si>
+  <si>
+    <t>/modules/09-Support_Vector_Machines.html</t>
+  </si>
+  <si>
+    <t>/modules/10-Principal_Component_Analysis.html</t>
+  </si>
+  <si>
+    <t>/modules/11-Cluster_Methodse.html</t>
+  </si>
+  <si>
+    <t>/modules/12-Missing_Data.html</t>
+  </si>
+  <si>
+    <t>/modules/13-Bayesian_Analysis.html</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
         <v>14</v>
@@ -1117,13 +1117,13 @@
         <v>46265</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1143,13 +1143,13 @@
         <v>46272</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1169,13 +1169,13 @@
         <v>46279</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1198,10 +1198,10 @@
         <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1224,10 +1224,10 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1250,10 +1250,10 @@
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1276,10 +1276,10 @@
         <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1302,10 +1302,10 @@
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1328,10 +1328,10 @@
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1354,10 +1354,10 @@
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1380,10 +1380,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1403,7 +1403,7 @@
         <v>46342</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1437,10 +1437,10 @@
         <v>46356</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1463,7 +1463,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA48E43-7BEE-F54B-BF68-736DF189B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B17B724-91CA-9944-B8C9-EDFADCF12662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
@@ -1065,7 +1065,7 @@
     <col min="2" max="3" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.83203125" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS382 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B17B724-91CA-9944-B8C9-EDFADCF12662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EDAC2C-CDD7-4742-8539-9117B253CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
+    <workbookView xWindow="2280" yWindow="7940" windowWidth="30240" windowHeight="18980" xr2:uid="{998DF6E3-BBDB-4446-B608-FEFD4AEC9D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Week</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Missing data</t>
   </si>
   <si>
-    <t>Introduction to the Modeling</t>
-  </si>
-  <si>
     <t>Project Proposal</t>
   </si>
   <si>
@@ -183,6 +180,15 @@
   </si>
   <si>
     <t>/modules/13-Bayesian_Analysis.html</t>
+  </si>
+  <si>
+    <t>00-Intro_to_Course</t>
+  </si>
+  <si>
+    <t>1JN7nhyWibw</t>
+  </si>
+  <si>
+    <t>Introduction to Predictive Modeling</t>
   </si>
 </sst>
 </file>
@@ -1067,6 +1073,7 @@
     <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -1117,13 +1124,19 @@
         <v>46265</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1146,7 +1159,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
         <v>21</v>
@@ -1172,7 +1185,7 @@
         <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
         <v>22</v>
@@ -1198,7 +1211,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
@@ -1224,7 +1237,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1250,7 +1263,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -1276,7 +1289,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -1302,7 +1315,7 @@
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -1328,7 +1341,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1354,7 +1367,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
@@ -1380,7 +1393,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -1403,7 +1416,7 @@
         <v>46342</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1440,7 +1453,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1463,7 +1476,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
